--- a/Result/profitability/4909.xlsx
+++ b/Result/profitability/4909.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7437499999999999</v>
+        <v>0.08124999999999996</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5975</v>
+        <v>-6.42375</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1625</v>
+        <v>-0.06625000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.016249999999999</v>
+        <v>-8.274999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01124999999999997</v>
+        <v>-0.01000000000000004</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.70875</v>
+        <v>-5.9575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04374999999999997</v>
+        <v>0.2925</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6662499999999998</v>
+        <v>-1.55375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3987499999999999</v>
+        <v>0.305</v>
       </c>
       <c r="N6" t="n">
-        <v>6.9825</v>
+        <v>2.7325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4712499999999999</v>
+        <v>0.42875</v>
       </c>
       <c r="N7" t="n">
-        <v>9.248750000000001</v>
+        <v>8.828750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5399999999999999</v>
+        <v>0.5175000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.76625</v>
+        <v>14.46125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9339,24 +9339,24 @@
         <v>52</v>
       </c>
       <c r="D71" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E71" t="n">
-        <v>-19</v>
+        <v>-9</v>
       </c>
       <c r="F71" t="n">
-        <v>-36.95</v>
+        <v>-17.88</v>
       </c>
       <c r="G71" t="n">
-        <v>-54</v>
+        <v>-44</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-104.10%</t>
+          <t>-85.03%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-153</v>
+        <v>-163</v>
       </c>
       <c r="J71" t="n">
         <v>-207</v>
@@ -9371,7 +9371,7 @@
         <v>1.05375</v>
       </c>
       <c r="N71" t="n">
-        <v>17.85625</v>
+        <v>20.24</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9404,10 +9404,10 @@
         <v>-54</v>
       </c>
       <c r="Y71" t="n">
-        <v>-37.96</v>
+        <v>-18.89</v>
       </c>
       <c r="Z71" t="n">
-        <v>-37.58415841584159</v>
+        <v>-18.7029702970297</v>
       </c>
       <c r="AA71" t="n">
         <v>-3.64</v>
@@ -9416,10 +9416,10 @@
         <v>-2.394736842105263</v>
       </c>
       <c r="AC71" t="n">
-        <v>-78.38</v>
+        <v>-59.31</v>
       </c>
       <c r="AD71" t="n">
-        <v>-1.891865797731113</v>
+        <v>-1.43157132512672</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9466,24 +9466,24 @@
         <v>71</v>
       </c>
       <c r="D72" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="F72" t="n">
-        <v>3.74</v>
+        <v>-10.05</v>
       </c>
       <c r="G72" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>23.54%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J72" t="n">
         <v>71</v>
@@ -9498,7 +9498,7 @@
         <v>1.05875</v>
       </c>
       <c r="N72" t="n">
-        <v>16.58125</v>
+        <v>17.24125</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9531,10 +9531,10 @@
         <v>-1.292452830188679</v>
       </c>
       <c r="Y72" t="n">
-        <v>40.69</v>
+        <v>7.829999999999998</v>
       </c>
       <c r="Z72" t="n">
-        <v>-1.101217861975643</v>
+        <v>-0.4379194630872483</v>
       </c>
       <c r="AA72" t="n">
         <v>-4.55</v>
@@ -9543,10 +9543,10 @@
         <v>-0.8800773694390716</v>
       </c>
       <c r="AC72" t="n">
-        <v>-35.45</v>
+        <v>-49.23999999999999</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.9045674917070681</v>
+        <v>-1.256442970145445</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9625,7 +9625,7 @@
         <v>1.1125</v>
       </c>
       <c r="N73" t="n">
-        <v>11.11625</v>
+        <v>11.77625</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9658,10 +9658,10 @@
         <v>-0.6612903225806452</v>
       </c>
       <c r="Y73" t="n">
-        <v>-30.64</v>
+        <v>-16.85</v>
       </c>
       <c r="Z73" t="n">
-        <v>-8.192513368983956</v>
+        <v>1.676616915422885</v>
       </c>
       <c r="AA73" t="n">
         <v>-1.49</v>
@@ -9752,7 +9752,7 @@
         <v>0.8987499999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>4.34875</v>
+        <v>5.008750000000001</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>52</v>
+      </c>
+      <c r="D75" t="n">
+        <v>67</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-30.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-57.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6924999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-3.9525</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5267406659939455</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9386792452830188</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.38</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6923937360178973</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
